--- a/output/chart_of_accounts.xlsx
+++ b/output/chart_of_accounts.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chart of Accounts" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Chart of Accounts" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <name val="Tahoma"/>
@@ -62,19 +59,13 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
     </border>
     <border>
       <left style="thin">
@@ -96,20 +87,20 @@
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -535,31 +526,31 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>1010</v>
+        <v>3000</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Leasehold Improvements</t>
+          <t>Equity Share Capital</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Non-current assets</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>Property, plant &amp; equipment</t>
+          <t>Share capital</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="G3" s="4" t="b">
@@ -568,26 +559,26 @@
     </row>
     <row r="4">
       <c r="A4" s="5" t="n">
-        <v>1015</v>
+        <v>3001</v>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Accumulated Depreciation - Leasehold Improvements</t>
+          <t>Preference Share Capital</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Non-current assets</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Property, plant &amp; equipment</t>
+          <t>Share capital</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -601,31 +592,31 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>1020</v>
+        <v>3010</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Furniture &amp; Fixtures</t>
+          <t>Securities Premium</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Non-current assets</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Property, plant &amp; equipment</t>
+          <t>Reserves &amp; surplus</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="G5" s="4" t="b">
@@ -634,26 +625,26 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
-        <v>1025</v>
+        <v>3020</v>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Accumulated Depreciation - Furniture &amp; Fixtures</t>
+          <t>Retained Earnings</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>Non-current assets</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>Property, plant &amp; equipment</t>
+          <t>Reserves &amp; surplus</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
@@ -667,31 +658,31 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>1030</v>
+        <v>3021</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Office Equipment</t>
+          <t>General Reserve</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Non-current assets</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Property, plant &amp; equipment</t>
+          <t>Reserves &amp; surplus</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="G7" s="4" t="b">
@@ -700,26 +691,26 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
-        <v>1035</v>
+        <v>3030</v>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>Accumulated Depreciation - Office Equipment</t>
+          <t>Current Year Profit &amp; Loss</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>Non-current assets</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>Property, plant &amp; equipment</t>
+          <t>Reserves &amp; surplus</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
@@ -733,31 +724,31 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>1040</v>
+        <v>3040</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Computers &amp; Laptops</t>
+          <t>Foreign Currency Translation Reserve</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Non-current assets</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Property, plant &amp; equipment</t>
+          <t>Other reserves</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="G9" s="4" t="b">
@@ -766,26 +757,26 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
-        <v>1045</v>
+        <v>3050</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Accumulated Depreciation - Computers &amp; Laptops</t>
+          <t>Remeasurement of Defined Benefit Plans (OCI)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>Non-current assets</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>Property, plant &amp; equipment</t>
+          <t>Other reserves</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
@@ -799,31 +790,31 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>1050</v>
+        <v>2000</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Servers &amp; Networking Equipment</t>
+          <t>Term Loan - HDFC Bank</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Non-current assets</t>
+          <t>Non-current liabilities</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Property, plant &amp; equipment</t>
+          <t>Borrowings</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="G11" s="4" t="b">
@@ -832,26 +823,26 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
-        <v>1055</v>
+        <v>2001</v>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Accumulated Depreciation - Servers &amp; Networking Equipment</t>
+          <t>Working Capital Loan (CC)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>Non-current assets</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>Property, plant &amp; equipment</t>
+          <t>Borrowings</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -865,31 +856,31 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>1060</v>
+        <v>2002</v>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Plant &amp; Machinery</t>
+          <t>Vehicle Loan</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Non-current assets</t>
+          <t>Non-current liabilities</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Property, plant &amp; equipment</t>
+          <t>Borrowings</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="G13" s="4" t="b">
@@ -898,26 +889,26 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
-        <v>1065</v>
+        <v>2010</v>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Accumulated Depreciation - Plant &amp; Machinery</t>
+          <t>Lease Liability - Non-current</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>Non-current assets</t>
+          <t>Non-current liabilities</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Property, plant &amp; equipment</t>
+          <t>Lease liabilities</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -931,31 +922,31 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>1070</v>
+        <v>2011</v>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Electrical Installations</t>
+          <t>Lease Liability - Current</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Non-current assets</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Property, plant &amp; equipment</t>
+          <t>Lease liabilities</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="G15" s="4" t="b">
@@ -964,26 +955,26 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
-        <v>1075</v>
+        <v>2100</v>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Accumulated Depreciation - Electrical Installations</t>
+          <t>Trade Payables - Goods</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>Non-current assets</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>Property, plant &amp; equipment</t>
+          <t>Trade payables</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -992,64 +983,64 @@
         </is>
       </c>
       <c r="G16" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>1080</v>
+        <v>2101</v>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Motor Vehicles</t>
+          <t>Trade Payables - Services</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Non-current assets</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Property, plant &amp; equipment</t>
+          <t>Trade payables</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="G17" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
-        <v>1085</v>
+        <v>2102</v>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Accumulated Depreciation - Motor Vehicles</t>
+          <t>Trade Payables - MSME</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>Non-current assets</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>Property, plant &amp; equipment</t>
+          <t>Trade payables</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -1058,64 +1049,64 @@
         </is>
       </c>
       <c r="G18" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>1100</v>
+        <v>2103</v>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Software Licences (Intangible)</t>
+          <t>Trade Payables - Import</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Non-current assets</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Intangible assets</t>
+          <t>Trade payables</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="G19" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
-        <v>1105</v>
+        <v>2110</v>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Accumulated Amortisation - Software</t>
+          <t>Creditors for Capital Goods</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>Non-current assets</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>Intangible assets</t>
+          <t>Trade payables</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
@@ -1124,36 +1115,36 @@
         </is>
       </c>
       <c r="G20" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>1110</v>
+        <v>2200</v>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Goodwill</t>
+          <t>Output CGST 0%</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Non-current assets</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Intangible assets</t>
+          <t>GST payable</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="G21" s="4" t="b">
@@ -1162,31 +1153,31 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="n">
-        <v>1120</v>
+        <v>2201</v>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Right-of-Use Asset - Office Premises</t>
+          <t>Output SGST 0%</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>Non-current assets</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>Right-of-use assets</t>
+          <t>GST payable</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="G22" s="6" t="b">
@@ -1195,31 +1186,31 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>1121</v>
+        <v>2202</v>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Right-of-Use Asset - Equipment</t>
+          <t>Output IGST 0%</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Non-current assets</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Right-of-use assets</t>
+          <t>GST payable</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="G23" s="4" t="b">
@@ -1228,26 +1219,26 @@
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
-        <v>1125</v>
+        <v>2203</v>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Accumulated Depreciation - ROU Assets</t>
+          <t>Output CGST 2.5%</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>Non-current assets</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>Right-of-use assets</t>
+          <t>GST payable</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
@@ -1261,31 +1252,31 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>1150</v>
+        <v>2204</v>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Security Deposits - Rent</t>
+          <t>Output SGST 2.5%</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Non-current assets</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Other financial assets</t>
+          <t>GST payable</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="G25" s="4" t="b">
@@ -1294,31 +1285,31 @@
     </row>
     <row r="26">
       <c r="A26" s="5" t="n">
-        <v>1151</v>
+        <v>2205</v>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>Security Deposits - Utilities</t>
+          <t>Output IGST 5%</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>Non-current assets</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>Other financial assets</t>
+          <t>GST payable</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="G26" s="6" t="b">
@@ -1327,31 +1318,31 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>1160</v>
+        <v>2206</v>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Deferred Tax Asset</t>
+          <t>Output CGST 6%</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Non-current assets</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Deferred tax</t>
+          <t>GST payable</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="G27" s="4" t="b">
@@ -1360,31 +1351,31 @@
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
-        <v>1170</v>
+        <v>2207</v>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Investment in Subsidiary - Middle East</t>
+          <t>Output SGST 6%</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>Non-current assets</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>Investments</t>
+          <t>GST payable</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="G28" s="6" t="b">
@@ -1393,92 +1384,92 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>1200</v>
+        <v>2208</v>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Trade Receivables - Domestic</t>
+          <t>Output IGST 12%</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Trade receivables</t>
+          <t>GST payable</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="G29" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
-        <v>1201</v>
+        <v>2209</v>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Trade Receivables - Export</t>
+          <t>Output CGST 9%</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>Trade receivables</t>
+          <t>GST payable</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="G30" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>1205</v>
+        <v>2210</v>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Allowance for Expected Credit Loss</t>
+          <t>Output SGST 9%</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Trade receivables</t>
+          <t>GST payable</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -1492,31 +1483,31 @@
     </row>
     <row r="32">
       <c r="A32" s="5" t="n">
-        <v>1210</v>
+        <v>2211</v>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Unbilled Revenue</t>
+          <t>Output IGST 18%</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>Trade receivables</t>
+          <t>GST payable</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="G32" s="6" t="b">
@@ -1525,31 +1516,31 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>1300</v>
+        <v>2212</v>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>HDFC Bank - Current A/c</t>
+          <t>Output CGST 14%</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Cash &amp; cash equivalents</t>
+          <t>GST payable</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="G33" s="4" t="b">
@@ -1558,31 +1549,31 @@
     </row>
     <row r="34">
       <c r="A34" s="5" t="n">
-        <v>1301</v>
+        <v>2213</v>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>ICICI Bank - Current A/c</t>
+          <t>Output SGST 14%</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>Cash &amp; cash equivalents</t>
+          <t>GST payable</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="G34" s="6" t="b">
@@ -1591,31 +1582,31 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>1302</v>
+        <v>2214</v>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Axis Bank - Current A/c</t>
+          <t>Output IGST 28%</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Cash &amp; cash equivalents</t>
+          <t>GST payable</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="G35" s="4" t="b">
@@ -1624,31 +1615,31 @@
     </row>
     <row r="36">
       <c r="A36" s="5" t="n">
-        <v>1303</v>
+        <v>2250</v>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>State Bank of India - Current A/c</t>
+          <t>GST Payable under RCM</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>Cash &amp; cash equivalents</t>
+          <t>GST payable</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="G36" s="6" t="b">
@@ -1657,31 +1648,31 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>1304</v>
+        <v>2251</v>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Kotak Mahindra Bank - Payroll A/c</t>
+          <t>GST Liability - Net Payable</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>Cash &amp; cash equivalents</t>
+          <t>GST payable</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="G37" s="4" t="b">
@@ -1690,31 +1681,31 @@
     </row>
     <row r="38">
       <c r="A38" s="5" t="n">
-        <v>1305</v>
+        <v>2300</v>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>HDFC Bank - EEFC A/c (USD)</t>
+          <t>TDS Payable - 192 (Salary)</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>Cash &amp; cash equivalents</t>
+          <t>Statutory dues</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="G38" s="6" t="b">
@@ -1723,31 +1714,31 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>1320</v>
+        <v>2301</v>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Cash in Hand</t>
+          <t>TDS Payable - 194C (Contractors)</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>Cash &amp; cash equivalents</t>
+          <t>Statutory dues</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="G39" s="4" t="b">
@@ -1756,31 +1747,31 @@
     </row>
     <row r="40">
       <c r="A40" s="5" t="n">
-        <v>1325</v>
+        <v>2302</v>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>Petty Cash</t>
+          <t>TDS Payable - 194J (Professional Fees)</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>Cash &amp; cash equivalents</t>
+          <t>Statutory dues</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="G40" s="6" t="b">
@@ -1789,31 +1780,31 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>1330</v>
+        <v>2303</v>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Fixed Deposits (&lt; 3 months)</t>
+          <t>TDS Payable - 194I (Rent)</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>Cash &amp; cash equivalents</t>
+          <t>Statutory dues</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="G41" s="4" t="b">
@@ -1822,31 +1813,31 @@
     </row>
     <row r="42">
       <c r="A42" s="5" t="n">
-        <v>1335</v>
+        <v>2304</v>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>Fixed Deposits (3-12 months)</t>
+          <t>TDS Payable - 194H (Commission)</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>Bank balances - other</t>
+          <t>Statutory dues</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="G42" s="6" t="b">
@@ -1855,31 +1846,31 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>1400</v>
+        <v>2305</v>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Input CGST 0%</t>
+          <t>TDS Payable - 194Q (Purchase of Goods)</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>GST input credit</t>
+          <t>Statutory dues</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="G43" s="4" t="b">
@@ -1888,31 +1879,31 @@
     </row>
     <row r="44">
       <c r="A44" s="5" t="n">
-        <v>1401</v>
+        <v>2306</v>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>Input SGST 0%</t>
+          <t>TDS Payable - 195 (Non-resident Payments)</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>GST input credit</t>
+          <t>Statutory dues</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="G44" s="6" t="b">
@@ -1921,31 +1912,31 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>1402</v>
+        <v>2320</v>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Input IGST 0%</t>
+          <t>TCS Payable - 206C</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>GST input credit</t>
+          <t>Statutory dues</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="G45" s="4" t="b">
@@ -1954,31 +1945,31 @@
     </row>
     <row r="46">
       <c r="A46" s="5" t="n">
-        <v>1403</v>
+        <v>2350</v>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>Input CGST 5%</t>
+          <t>PF Payable (Employee + Employer)</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>GST input credit</t>
+          <t>Statutory dues</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="G46" s="6" t="b">
@@ -1987,31 +1978,31 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>1404</v>
+        <v>2351</v>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Input SGST 5%</t>
+          <t>ESI Payable</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>GST input credit</t>
+          <t>Statutory dues</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="G47" s="4" t="b">
@@ -2020,31 +2011,31 @@
     </row>
     <row r="48">
       <c r="A48" s="5" t="n">
-        <v>1405</v>
+        <v>2352</v>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>Input IGST 5%</t>
+          <t>Professional Tax Payable</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>GST input credit</t>
+          <t>Statutory dues</t>
         </is>
       </c>
       <c r="F48" s="6" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="G48" s="6" t="b">
@@ -2053,31 +2044,31 @@
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>1406</v>
+        <v>2353</v>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Input CGST 12%</t>
+          <t>Labour Welfare Fund Payable</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>GST input credit</t>
+          <t>Statutory dues</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="G49" s="4" t="b">
@@ -2086,31 +2077,31 @@
     </row>
     <row r="50">
       <c r="A50" s="5" t="n">
-        <v>1407</v>
+        <v>2354</v>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>Input SGST 12%</t>
+          <t>NPS Payable (Employer)</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>GST input credit</t>
+          <t>Statutory dues</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="G50" s="6" t="b">
@@ -2119,31 +2110,31 @@
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>1408</v>
+        <v>2400</v>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Input IGST 12%</t>
+          <t>Salaries Payable</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>GST input credit</t>
+          <t>Employee benefits</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="G51" s="4" t="b">
@@ -2152,31 +2143,31 @@
     </row>
     <row r="52">
       <c r="A52" s="5" t="n">
-        <v>1409</v>
+        <v>2401</v>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>Input CGST 18%</t>
+          <t>Bonus Payable</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>GST input credit</t>
+          <t>Employee benefits</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="G52" s="6" t="b">
@@ -2185,31 +2176,31 @@
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>1410</v>
+        <v>2402</v>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Input SGST 18%</t>
+          <t>Reimbursements Payable</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>GST input credit</t>
+          <t>Employee benefits</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="G53" s="4" t="b">
@@ -2218,31 +2209,31 @@
     </row>
     <row r="54">
       <c r="A54" s="5" t="n">
-        <v>1411</v>
+        <v>2410</v>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>Input IGST 18%</t>
+          <t>Provision for Gratuity</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Non-current liabilities</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>GST input credit</t>
+          <t>Employee benefits</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="G54" s="6" t="b">
@@ -2251,31 +2242,31 @@
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>1412</v>
+        <v>2411</v>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Input CGST 28%</t>
+          <t>Provision for Leave Encashment</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Non-current liabilities</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>GST input credit</t>
+          <t>Employee benefits</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="G55" s="4" t="b">
@@ -2284,31 +2275,31 @@
     </row>
     <row r="56">
       <c r="A56" s="5" t="n">
-        <v>1413</v>
+        <v>2500</v>
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>Input SGST 28%</t>
+          <t>Accrued Expenses</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>GST input credit</t>
+          <t>Other current liabilities</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="G56" s="6" t="b">
@@ -2317,64 +2308,64 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>1414</v>
+        <v>2501</v>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Input IGST 28%</t>
+          <t>Advance from Customers</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>GST input credit</t>
+          <t>Other current liabilities</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="G57" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="n">
-        <v>1450</v>
+        <v>2502</v>
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>GST Electronic Cash Ledger</t>
+          <t>Deferred Revenue (Unearned)</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>GST input credit</t>
+          <t>Other current liabilities</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="G58" s="6" t="b">
@@ -2383,64 +2374,64 @@
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>1451</v>
+        <v>2503</v>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>GST Input Credit (Provisional / ineligible)</t>
+          <t>Payable to Group Companies</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>GST input credit</t>
+          <t>Other current liabilities</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="G59" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="n">
-        <v>1460</v>
+        <v>2510</v>
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>TDS Receivable (26AS)</t>
+          <t>Provision for Income Tax</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>Other tax assets</t>
+          <t>Provisions</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="G60" s="6" t="b">
@@ -2449,31 +2440,31 @@
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>1461</v>
+        <v>2511</v>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>TCS Receivable</t>
+          <t>Provision for Audit Fees</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>Other tax assets</t>
+          <t>Provisions</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="G61" s="4" t="b">
@@ -2482,31 +2473,31 @@
     </row>
     <row r="62">
       <c r="A62" s="5" t="n">
-        <v>1462</v>
+        <v>2512</v>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>Advance Income Tax</t>
+          <t>Provision for Expenses</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>Other tax assets</t>
+          <t>Provisions</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="G62" s="6" t="b">
@@ -2515,31 +2506,31 @@
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>1463</v>
+        <v>2520</v>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Income Tax Refund Due</t>
+          <t>Deferred Tax Liability</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Non-current liabilities</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>Other tax assets</t>
+          <t>Deferred tax</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="G63" s="4" t="b">
@@ -2548,11 +2539,11 @@
     </row>
     <row r="64">
       <c r="A64" s="5" t="n">
-        <v>1500</v>
+        <v>1010</v>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>Inventory - Consumables</t>
+          <t>Leasehold Improvements</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
@@ -2562,12 +2553,12 @@
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Non-current assets</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>Inventories</t>
+          <t>Property, plant &amp; equipment</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr">
@@ -2581,11 +2572,11 @@
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>1501</v>
+        <v>1015</v>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Inventory - Spares</t>
+          <t>Accumulated Depreciation - Leasehold Improvements</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -2595,17 +2586,17 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Non-current assets</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>Inventories</t>
+          <t>Property, plant &amp; equipment</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="G65" s="4" t="b">
@@ -2614,11 +2605,11 @@
     </row>
     <row r="66">
       <c r="A66" s="5" t="n">
-        <v>1550</v>
+        <v>1020</v>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>Advance to Vendors</t>
+          <t>Furniture &amp; Fixtures</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
@@ -2628,12 +2619,12 @@
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Non-current assets</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>Other current assets</t>
+          <t>Property, plant &amp; equipment</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr">
@@ -2642,16 +2633,16 @@
         </is>
       </c>
       <c r="G66" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>1551</v>
+        <v>1025</v>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Advance to Employees</t>
+          <t>Accumulated Depreciation - Furniture &amp; Fixtures</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -2661,17 +2652,17 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Non-current assets</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>Other current assets</t>
+          <t>Property, plant &amp; equipment</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="G67" s="4" t="b">
@@ -2680,11 +2671,11 @@
     </row>
     <row r="68">
       <c r="A68" s="5" t="n">
-        <v>1552</v>
+        <v>1030</v>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>Prepaid Insurance</t>
+          <t>Office Equipment</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
@@ -2694,12 +2685,12 @@
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Non-current assets</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>Other current assets</t>
+          <t>Property, plant &amp; equipment</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr">
@@ -2713,11 +2704,11 @@
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>1553</v>
+        <v>1035</v>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Prepaid Software Subscriptions</t>
+          <t>Accumulated Depreciation - Office Equipment</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -2727,17 +2718,17 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Non-current assets</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>Other current assets</t>
+          <t>Property, plant &amp; equipment</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="G69" s="4" t="b">
@@ -2746,11 +2737,11 @@
     </row>
     <row r="70">
       <c r="A70" s="5" t="n">
-        <v>1554</v>
+        <v>1040</v>
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>Prepaid Rent</t>
+          <t>Computers &amp; Laptops</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
@@ -2760,12 +2751,12 @@
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Non-current assets</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>Other current assets</t>
+          <t>Property, plant &amp; equipment</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr">
@@ -2779,11 +2770,11 @@
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>1555</v>
+        <v>1045</v>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Prepaid AMC</t>
+          <t>Accumulated Depreciation - Computers &amp; Laptops</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -2793,17 +2784,17 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Non-current assets</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>Other current assets</t>
+          <t>Property, plant &amp; equipment</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="G71" s="4" t="b">
@@ -2812,11 +2803,11 @@
     </row>
     <row r="72">
       <c r="A72" s="5" t="n">
-        <v>1560</v>
+        <v>1050</v>
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>GST Refund Receivable (Export/LUT)</t>
+          <t>Servers &amp; Networking Equipment</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
@@ -2826,12 +2817,12 @@
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Non-current assets</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>Other current assets</t>
+          <t>Property, plant &amp; equipment</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr">
@@ -2845,11 +2836,11 @@
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
-        <v>1561</v>
+        <v>1055</v>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Receivable from Group Companies</t>
+          <t>Accumulated Depreciation - Servers &amp; Networking Equipment</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -2859,50 +2850,50 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Non-current assets</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>Other current assets</t>
+          <t>Property, plant &amp; equipment</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="G73" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="n">
-        <v>2000</v>
+        <v>1060</v>
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>Term Loan - HDFC Bank</t>
+          <t>Plant &amp; Machinery</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>Non-current liabilities</t>
+          <t>Non-current assets</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>Borrowings</t>
+          <t>Property, plant &amp; equipment</t>
         </is>
       </c>
       <c r="F74" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="G74" s="6" t="b">
@@ -2911,26 +2902,26 @@
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
-        <v>2001</v>
+        <v>1065</v>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Working Capital Loan (CC)</t>
+          <t>Accumulated Depreciation - Plant &amp; Machinery</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Non-current assets</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>Borrowings</t>
+          <t>Property, plant &amp; equipment</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
@@ -2944,31 +2935,31 @@
     </row>
     <row r="76">
       <c r="A76" s="5" t="n">
-        <v>2002</v>
+        <v>1070</v>
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>Vehicle Loan</t>
+          <t>Electrical Installations</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>Non-current liabilities</t>
+          <t>Non-current assets</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>Borrowings</t>
+          <t>Property, plant &amp; equipment</t>
         </is>
       </c>
       <c r="F76" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="G76" s="6" t="b">
@@ -2977,26 +2968,26 @@
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
-        <v>2010</v>
+        <v>1075</v>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Lease Liability - Non-current</t>
+          <t>Accumulated Depreciation - Electrical Installations</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>Non-current liabilities</t>
+          <t>Non-current assets</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>Lease liabilities</t>
+          <t>Property, plant &amp; equipment</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
@@ -3010,31 +3001,31 @@
     </row>
     <row r="78">
       <c r="A78" s="5" t="n">
-        <v>2011</v>
+        <v>1080</v>
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>Lease Liability - Current</t>
+          <t>Motor Vehicles</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Non-current assets</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>Lease liabilities</t>
+          <t>Property, plant &amp; equipment</t>
         </is>
       </c>
       <c r="F78" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="G78" s="6" t="b">
@@ -3043,26 +3034,26 @@
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
-        <v>2100</v>
+        <v>1085</v>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Trade Payables - Goods</t>
+          <t>Accumulated Depreciation - Motor Vehicles</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Non-current assets</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>Trade payables</t>
+          <t>Property, plant &amp; equipment</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
@@ -3071,64 +3062,64 @@
         </is>
       </c>
       <c r="G79" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="n">
-        <v>2101</v>
+        <v>1100</v>
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>Trade Payables - Services</t>
+          <t>Software Licences (Intangible)</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Non-current assets</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>Trade payables</t>
+          <t>Intangible assets</t>
         </is>
       </c>
       <c r="F80" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="G80" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
-        <v>2102</v>
+        <v>1105</v>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Trade Payables - MSME</t>
+          <t>Accumulated Amortisation - Software</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Non-current assets</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>Trade payables</t>
+          <t>Intangible assets</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
@@ -3137,102 +3128,102 @@
         </is>
       </c>
       <c r="G81" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="n">
-        <v>2103</v>
+        <v>1110</v>
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>Trade Payables - Import</t>
+          <t>Goodwill</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Non-current assets</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>Trade payables</t>
+          <t>Intangible assets</t>
         </is>
       </c>
       <c r="F82" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="G82" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="n">
-        <v>2110</v>
+        <v>1120</v>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Creditors for Capital Goods</t>
+          <t>Right-of-Use Asset - Office Premises</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Non-current assets</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>Trade payables</t>
+          <t>Right-of-use assets</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="G83" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="n">
-        <v>2200</v>
+        <v>1121</v>
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>Output CGST 0%</t>
+          <t>Right-of-Use Asset - Equipment</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Non-current assets</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>GST payable</t>
+          <t>Right-of-use assets</t>
         </is>
       </c>
       <c r="F84" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="G84" s="6" t="b">
@@ -3241,26 +3232,26 @@
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
-        <v>2201</v>
+        <v>1125</v>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Output SGST 0%</t>
+          <t>Accumulated Depreciation - ROU Assets</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Non-current assets</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>GST payable</t>
+          <t>Right-of-use assets</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
@@ -3274,31 +3265,31 @@
     </row>
     <row r="86">
       <c r="A86" s="5" t="n">
-        <v>2202</v>
+        <v>1150</v>
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>Output IGST 0%</t>
+          <t>Security Deposits - Rent</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Non-current assets</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t>GST payable</t>
+          <t>Other financial assets</t>
         </is>
       </c>
       <c r="F86" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="G86" s="6" t="b">
@@ -3307,31 +3298,31 @@
     </row>
     <row r="87">
       <c r="A87" s="3" t="n">
-        <v>2203</v>
+        <v>1151</v>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Output CGST 5%</t>
+          <t>Security Deposits - Utilities</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Non-current assets</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>GST payable</t>
+          <t>Other financial assets</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="G87" s="4" t="b">
@@ -3340,31 +3331,31 @@
     </row>
     <row r="88">
       <c r="A88" s="5" t="n">
-        <v>2204</v>
+        <v>1160</v>
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>Output SGST 5%</t>
+          <t>Deferred Tax Asset</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Non-current assets</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
         <is>
-          <t>GST payable</t>
+          <t>Deferred tax</t>
         </is>
       </c>
       <c r="F88" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="G88" s="6" t="b">
@@ -3373,31 +3364,31 @@
     </row>
     <row r="89">
       <c r="A89" s="3" t="n">
-        <v>2205</v>
+        <v>1170</v>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Output IGST 5%</t>
+          <t>Investment in Subsidiary - Middle East</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Non-current assets</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>GST payable</t>
+          <t>Investments</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="G89" s="4" t="b">
@@ -3406,92 +3397,92 @@
     </row>
     <row r="90">
       <c r="A90" s="5" t="n">
-        <v>2206</v>
+        <v>1200</v>
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>Output CGST 12%</t>
+          <t>Trade Receivables - Domestic</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>GST payable</t>
+          <t>Trade receivables</t>
         </is>
       </c>
       <c r="F90" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="G90" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="n">
-        <v>2207</v>
+        <v>1201</v>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Output SGST 12%</t>
+          <t>Trade Receivables - Export</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>GST payable</t>
+          <t>Trade receivables</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="G91" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="n">
-        <v>2208</v>
+        <v>1205</v>
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>Output IGST 12%</t>
+          <t>Allowance for Expected Credit Loss</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
         <is>
-          <t>GST payable</t>
+          <t>Trade receivables</t>
         </is>
       </c>
       <c r="F92" s="6" t="inlineStr">
@@ -3505,31 +3496,31 @@
     </row>
     <row r="93">
       <c r="A93" s="3" t="n">
-        <v>2209</v>
+        <v>1210</v>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Output CGST 18%</t>
+          <t>Unbilled Revenue</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>GST payable</t>
+          <t>Trade receivables</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="G93" s="4" t="b">
@@ -3538,31 +3529,31 @@
     </row>
     <row r="94">
       <c r="A94" s="5" t="n">
-        <v>2210</v>
+        <v>1300</v>
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>Output SGST 18%</t>
+          <t>HDFC Bank - Current A/c</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
         <is>
-          <t>GST payable</t>
+          <t>Cash &amp; cash equivalents</t>
         </is>
       </c>
       <c r="F94" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="G94" s="6" t="b">
@@ -3571,31 +3562,31 @@
     </row>
     <row r="95">
       <c r="A95" s="3" t="n">
-        <v>2211</v>
+        <v>1301</v>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Output IGST 18%</t>
+          <t>ICICI Bank - Current A/c</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>GST payable</t>
+          <t>Cash &amp; cash equivalents</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="G95" s="4" t="b">
@@ -3604,31 +3595,31 @@
     </row>
     <row r="96">
       <c r="A96" s="5" t="n">
-        <v>2212</v>
+        <v>1302</v>
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>Output CGST 28%</t>
+          <t>Axis Bank - Current A/c</t>
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
         <is>
-          <t>GST payable</t>
+          <t>Cash &amp; cash equivalents</t>
         </is>
       </c>
       <c r="F96" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="G96" s="6" t="b">
@@ -3637,31 +3628,31 @@
     </row>
     <row r="97">
       <c r="A97" s="3" t="n">
-        <v>2213</v>
+        <v>1303</v>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Output SGST 28%</t>
+          <t>State Bank of India - Current A/c</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>GST payable</t>
+          <t>Cash &amp; cash equivalents</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="G97" s="4" t="b">
@@ -3670,31 +3661,31 @@
     </row>
     <row r="98">
       <c r="A98" s="5" t="n">
-        <v>2214</v>
+        <v>1304</v>
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>Output IGST 28%</t>
+          <t>Kotak Mahindra Bank - Payroll A/c</t>
         </is>
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
         <is>
-          <t>GST payable</t>
+          <t>Cash &amp; cash equivalents</t>
         </is>
       </c>
       <c r="F98" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="G98" s="6" t="b">
@@ -3703,31 +3694,31 @@
     </row>
     <row r="99">
       <c r="A99" s="3" t="n">
-        <v>2250</v>
+        <v>1305</v>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>GST Payable under RCM</t>
+          <t>HDFC Bank - EEFC A/c (USD)</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>GST payable</t>
+          <t>Cash &amp; cash equivalents</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="G99" s="4" t="b">
@@ -3736,31 +3727,31 @@
     </row>
     <row r="100">
       <c r="A100" s="5" t="n">
-        <v>2251</v>
+        <v>1320</v>
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>GST Liability - Net Payable</t>
+          <t>Cash in Hand</t>
         </is>
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
         <is>
-          <t>GST payable</t>
+          <t>Cash &amp; cash equivalents</t>
         </is>
       </c>
       <c r="F100" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="G100" s="6" t="b">
@@ -3769,31 +3760,31 @@
     </row>
     <row r="101">
       <c r="A101" s="3" t="n">
-        <v>2300</v>
+        <v>1325</v>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>TDS Payable - 192 (Salary)</t>
+          <t>Petty Cash</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>Statutory dues</t>
+          <t>Cash &amp; cash equivalents</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="G101" s="4" t="b">
@@ -3802,31 +3793,31 @@
     </row>
     <row r="102">
       <c r="A102" s="5" t="n">
-        <v>2301</v>
+        <v>1330</v>
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>TDS Payable - 194C (Contractors)</t>
+          <t>Fixed Deposits (&lt; 3 months)</t>
         </is>
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
         <is>
-          <t>Statutory dues</t>
+          <t>Cash &amp; cash equivalents</t>
         </is>
       </c>
       <c r="F102" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="G102" s="6" t="b">
@@ -3835,31 +3826,31 @@
     </row>
     <row r="103">
       <c r="A103" s="3" t="n">
-        <v>2302</v>
+        <v>1335</v>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>TDS Payable - 194J (Professional Fees)</t>
+          <t>Fixed Deposits (3-12 months)</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>Statutory dues</t>
+          <t>Bank balances - other</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="G103" s="4" t="b">
@@ -3868,31 +3859,31 @@
     </row>
     <row r="104">
       <c r="A104" s="5" t="n">
-        <v>2303</v>
+        <v>1400</v>
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>TDS Payable - 194I (Rent)</t>
+          <t>Input CGST 0%</t>
         </is>
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D104" s="6" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
         <is>
-          <t>Statutory dues</t>
+          <t>GST input credit</t>
         </is>
       </c>
       <c r="F104" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="G104" s="6" t="b">
@@ -3901,31 +3892,31 @@
     </row>
     <row r="105">
       <c r="A105" s="3" t="n">
-        <v>2304</v>
+        <v>1401</v>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>TDS Payable - 194H (Commission)</t>
+          <t>Input SGST 0%</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>Statutory dues</t>
+          <t>GST input credit</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="G105" s="4" t="b">
@@ -3934,31 +3925,31 @@
     </row>
     <row r="106">
       <c r="A106" s="5" t="n">
-        <v>2305</v>
+        <v>1402</v>
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>TDS Payable - 194Q (Purchase of Goods)</t>
+          <t>Input IGST 0%</t>
         </is>
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D106" s="6" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
         <is>
-          <t>Statutory dues</t>
+          <t>GST input credit</t>
         </is>
       </c>
       <c r="F106" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="G106" s="6" t="b">
@@ -3967,31 +3958,31 @@
     </row>
     <row r="107">
       <c r="A107" s="3" t="n">
-        <v>2306</v>
+        <v>1403</v>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>TDS Payable - 195 (Non-resident Payments)</t>
+          <t>Input CGST 2.5%</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>Statutory dues</t>
+          <t>GST input credit</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="G107" s="4" t="b">
@@ -4000,31 +3991,31 @@
     </row>
     <row r="108">
       <c r="A108" s="5" t="n">
-        <v>2320</v>
+        <v>1404</v>
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>TCS Payable - 206C</t>
+          <t>Input SGST 2.5%</t>
         </is>
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D108" s="6" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
         <is>
-          <t>Statutory dues</t>
+          <t>GST input credit</t>
         </is>
       </c>
       <c r="F108" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="G108" s="6" t="b">
@@ -4033,31 +4024,31 @@
     </row>
     <row r="109">
       <c r="A109" s="3" t="n">
-        <v>2350</v>
+        <v>1405</v>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>PF Payable (Employee + Employer)</t>
+          <t>Input IGST 5%</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>Statutory dues</t>
+          <t>GST input credit</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="G109" s="4" t="b">
@@ -4066,31 +4057,31 @@
     </row>
     <row r="110">
       <c r="A110" s="5" t="n">
-        <v>2351</v>
+        <v>1406</v>
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>ESI Payable</t>
+          <t>Input CGST 6%</t>
         </is>
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D110" s="6" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="E110" s="6" t="inlineStr">
         <is>
-          <t>Statutory dues</t>
+          <t>GST input credit</t>
         </is>
       </c>
       <c r="F110" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="G110" s="6" t="b">
@@ -4099,31 +4090,31 @@
     </row>
     <row r="111">
       <c r="A111" s="3" t="n">
-        <v>2352</v>
+        <v>1407</v>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>Professional Tax Payable</t>
+          <t>Input SGST 6%</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>Statutory dues</t>
+          <t>GST input credit</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="G111" s="4" t="b">
@@ -4132,31 +4123,31 @@
     </row>
     <row r="112">
       <c r="A112" s="5" t="n">
-        <v>2353</v>
+        <v>1408</v>
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>Labour Welfare Fund Payable</t>
+          <t>Input IGST 12%</t>
         </is>
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D112" s="6" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="E112" s="6" t="inlineStr">
         <is>
-          <t>Statutory dues</t>
+          <t>GST input credit</t>
         </is>
       </c>
       <c r="F112" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="G112" s="6" t="b">
@@ -4165,31 +4156,31 @@
     </row>
     <row r="113">
       <c r="A113" s="3" t="n">
-        <v>2354</v>
+        <v>1409</v>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>NPS Payable (Employer)</t>
+          <t>Input CGST 9%</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>Statutory dues</t>
+          <t>GST input credit</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="G113" s="4" t="b">
@@ -4198,31 +4189,31 @@
     </row>
     <row r="114">
       <c r="A114" s="5" t="n">
-        <v>2400</v>
+        <v>1410</v>
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>Salaries Payable</t>
+          <t>Input SGST 9%</t>
         </is>
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D114" s="6" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="E114" s="6" t="inlineStr">
         <is>
-          <t>Employee benefits</t>
+          <t>GST input credit</t>
         </is>
       </c>
       <c r="F114" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="G114" s="6" t="b">
@@ -4231,31 +4222,31 @@
     </row>
     <row r="115">
       <c r="A115" s="3" t="n">
-        <v>2401</v>
+        <v>1411</v>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>Bonus Payable</t>
+          <t>Input IGST 18%</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>Employee benefits</t>
+          <t>GST input credit</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="G115" s="4" t="b">
@@ -4264,31 +4255,31 @@
     </row>
     <row r="116">
       <c r="A116" s="5" t="n">
-        <v>2402</v>
+        <v>1412</v>
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>Reimbursements Payable</t>
+          <t>Input CGST 14%</t>
         </is>
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D116" s="6" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="E116" s="6" t="inlineStr">
         <is>
-          <t>Employee benefits</t>
+          <t>GST input credit</t>
         </is>
       </c>
       <c r="F116" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="G116" s="6" t="b">
@@ -4297,31 +4288,31 @@
     </row>
     <row r="117">
       <c r="A117" s="3" t="n">
-        <v>2410</v>
+        <v>1413</v>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>Provision for Gratuity</t>
+          <t>Input SGST 14%</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>Non-current liabilities</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>Employee benefits</t>
+          <t>GST input credit</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="G117" s="4" t="b">
@@ -4330,31 +4321,31 @@
     </row>
     <row r="118">
       <c r="A118" s="5" t="n">
-        <v>2411</v>
+        <v>1414</v>
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>Provision for Leave Encashment</t>
+          <t>Input IGST 28%</t>
         </is>
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D118" s="6" t="inlineStr">
         <is>
-          <t>Non-current liabilities</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="E118" s="6" t="inlineStr">
         <is>
-          <t>Employee benefits</t>
+          <t>GST input credit</t>
         </is>
       </c>
       <c r="F118" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="G118" s="6" t="b">
@@ -4363,31 +4354,31 @@
     </row>
     <row r="119">
       <c r="A119" s="3" t="n">
-        <v>2500</v>
+        <v>1450</v>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>Accrued Expenses</t>
+          <t>GST Electronic Cash Ledger</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>Other current liabilities</t>
+          <t>GST input credit</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="G119" s="4" t="b">
@@ -4396,64 +4387,64 @@
     </row>
     <row r="120">
       <c r="A120" s="5" t="n">
-        <v>2501</v>
+        <v>1451</v>
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>Advance from Customers</t>
+          <t>GST Input Credit (Provisional / ineligible)</t>
         </is>
       </c>
       <c r="C120" s="6" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D120" s="6" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="E120" s="6" t="inlineStr">
         <is>
-          <t>Other current liabilities</t>
+          <t>GST input credit</t>
         </is>
       </c>
       <c r="F120" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="G120" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="n">
-        <v>2502</v>
+        <v>1460</v>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>Deferred Revenue (Unearned)</t>
+          <t>TDS Receivable (26AS)</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>Other current liabilities</t>
+          <t>Other tax assets</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="G121" s="4" t="b">
@@ -4462,64 +4453,64 @@
     </row>
     <row r="122">
       <c r="A122" s="5" t="n">
-        <v>2503</v>
+        <v>1461</v>
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>Payable to Group Companies</t>
+          <t>TCS Receivable</t>
         </is>
       </c>
       <c r="C122" s="6" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D122" s="6" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
-          <t>Other current liabilities</t>
+          <t>Other tax assets</t>
         </is>
       </c>
       <c r="F122" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="G122" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="n">
-        <v>2510</v>
+        <v>1462</v>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>Provision for Income Tax</t>
+          <t>Advance Income Tax</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>Provisions</t>
+          <t>Other tax assets</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="G123" s="4" t="b">
@@ -4528,31 +4519,31 @@
     </row>
     <row r="124">
       <c r="A124" s="5" t="n">
-        <v>2511</v>
+        <v>1463</v>
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>Provision for Audit Fees</t>
+          <t>Income Tax Refund Due</t>
         </is>
       </c>
       <c r="C124" s="6" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D124" s="6" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="E124" s="6" t="inlineStr">
         <is>
-          <t>Provisions</t>
+          <t>Other tax assets</t>
         </is>
       </c>
       <c r="F124" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="G124" s="6" t="b">
@@ -4561,31 +4552,31 @@
     </row>
     <row r="125">
       <c r="A125" s="3" t="n">
-        <v>2512</v>
+        <v>1500</v>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>Provision for Expenses</t>
+          <t>Inventory - Consumables</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>Provisions</t>
+          <t>Inventories</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="G125" s="4" t="b">
@@ -4594,31 +4585,31 @@
     </row>
     <row r="126">
       <c r="A126" s="5" t="n">
-        <v>2520</v>
+        <v>1501</v>
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>Deferred Tax Liability</t>
+          <t>Inventory - Spares</t>
         </is>
       </c>
       <c r="C126" s="6" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D126" s="6" t="inlineStr">
         <is>
-          <t>Non-current liabilities</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="E126" s="6" t="inlineStr">
         <is>
-          <t>Deferred tax</t>
+          <t>Inventories</t>
         </is>
       </c>
       <c r="F126" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="G126" s="6" t="b">
@@ -4627,64 +4618,64 @@
     </row>
     <row r="127">
       <c r="A127" s="3" t="n">
-        <v>3000</v>
+        <v>1550</v>
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>Equity Share Capital</t>
+          <t>Advance to Vendors</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>Equity</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>Equity</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>Share capital</t>
+          <t>Other current assets</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="G127" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="5" t="n">
-        <v>3001</v>
+        <v>1551</v>
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>Preference Share Capital</t>
+          <t>Advance to Employees</t>
         </is>
       </c>
       <c r="C128" s="6" t="inlineStr">
         <is>
-          <t>Equity</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D128" s="6" t="inlineStr">
         <is>
-          <t>Equity</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="E128" s="6" t="inlineStr">
         <is>
-          <t>Share capital</t>
+          <t>Other current assets</t>
         </is>
       </c>
       <c r="F128" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="G128" s="6" t="b">
@@ -4693,31 +4684,31 @@
     </row>
     <row r="129">
       <c r="A129" s="3" t="n">
-        <v>3010</v>
+        <v>1552</v>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>Securities Premium</t>
+          <t>Prepaid Insurance</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>Equity</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>Equity</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>Reserves &amp; surplus</t>
+          <t>Other current assets</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="G129" s="4" t="b">
@@ -4726,31 +4717,31 @@
     </row>
     <row r="130">
       <c r="A130" s="5" t="n">
-        <v>3020</v>
+        <v>1553</v>
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>Retained Earnings</t>
+          <t>Prepaid Software Subscriptions</t>
         </is>
       </c>
       <c r="C130" s="6" t="inlineStr">
         <is>
-          <t>Equity</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D130" s="6" t="inlineStr">
         <is>
-          <t>Equity</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="E130" s="6" t="inlineStr">
         <is>
-          <t>Reserves &amp; surplus</t>
+          <t>Other current assets</t>
         </is>
       </c>
       <c r="F130" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="G130" s="6" t="b">
@@ -4759,31 +4750,31 @@
     </row>
     <row r="131">
       <c r="A131" s="3" t="n">
-        <v>3021</v>
+        <v>1554</v>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>General Reserve</t>
+          <t>Prepaid Rent</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>Equity</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>Equity</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>Reserves &amp; surplus</t>
+          <t>Other current assets</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="G131" s="4" t="b">
@@ -4792,31 +4783,31 @@
     </row>
     <row r="132">
       <c r="A132" s="5" t="n">
-        <v>3030</v>
+        <v>1555</v>
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>Current Year Profit &amp; Loss</t>
+          <t>Prepaid AMC</t>
         </is>
       </c>
       <c r="C132" s="6" t="inlineStr">
         <is>
-          <t>Equity</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D132" s="6" t="inlineStr">
         <is>
-          <t>Equity</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="E132" s="6" t="inlineStr">
         <is>
-          <t>Reserves &amp; surplus</t>
+          <t>Other current assets</t>
         </is>
       </c>
       <c r="F132" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="G132" s="6" t="b">
@@ -4825,31 +4816,31 @@
     </row>
     <row r="133">
       <c r="A133" s="3" t="n">
-        <v>3040</v>
+        <v>1560</v>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>Foreign Currency Translation Reserve</t>
+          <t>GST Refund Receivable (Export/LUT)</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>Equity</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>Equity</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>Other reserves</t>
+          <t>Other current assets</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="G133" s="4" t="b">
@@ -4858,35 +4849,35 @@
     </row>
     <row r="134">
       <c r="A134" s="5" t="n">
-        <v>3050</v>
+        <v>1561</v>
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>Remeasurement of Defined Benefit Plans (OCI)</t>
+          <t>Receivable from Group Companies</t>
         </is>
       </c>
       <c r="C134" s="6" t="inlineStr">
         <is>
-          <t>Equity</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D134" s="6" t="inlineStr">
         <is>
-          <t>Equity</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="E134" s="6" t="inlineStr">
         <is>
-          <t>Other reserves</t>
+          <t>Other current assets</t>
         </is>
       </c>
       <c r="F134" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="G134" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135">

--- a/output/chart_of_accounts.xlsx
+++ b/output/chart_of_accounts.xlsx
@@ -526,7 +526,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
@@ -559,7 +559,7 @@
     </row>
     <row r="4">
       <c r="A4" s="5" t="n">
-        <v>3001</v>
+        <v>1001</v>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
@@ -592,7 +592,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>3010</v>
+        <v>1010</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
@@ -625,7 +625,7 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
-        <v>3020</v>
+        <v>1020</v>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>3021</v>
+        <v>1021</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
-        <v>3030</v>
+        <v>1030</v>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>3040</v>
+        <v>1040</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
-        <v>3050</v>
+        <v>1050</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
     </row>
     <row r="64">
       <c r="A64" s="5" t="n">
-        <v>1010</v>
+        <v>3010</v>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>1015</v>
+        <v>3015</v>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
     </row>
     <row r="66">
       <c r="A66" s="5" t="n">
-        <v>1020</v>
+        <v>3020</v>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>1025</v>
+        <v>3025</v>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
     </row>
     <row r="68">
       <c r="A68" s="5" t="n">
-        <v>1030</v>
+        <v>3030</v>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>1035</v>
+        <v>3035</v>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
     </row>
     <row r="70">
       <c r="A70" s="5" t="n">
-        <v>1040</v>
+        <v>3040</v>
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>1045</v>
+        <v>3045</v>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
     </row>
     <row r="72">
       <c r="A72" s="5" t="n">
-        <v>1050</v>
+        <v>3050</v>
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
@@ -2836,7 +2836,7 @@
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
-        <v>1055</v>
+        <v>3055</v>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
     </row>
     <row r="74">
       <c r="A74" s="5" t="n">
-        <v>1060</v>
+        <v>3060</v>
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
-        <v>1065</v>
+        <v>3065</v>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
     </row>
     <row r="76">
       <c r="A76" s="5" t="n">
-        <v>1070</v>
+        <v>3070</v>
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
-        <v>1075</v>
+        <v>3075</v>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
     </row>
     <row r="78">
       <c r="A78" s="5" t="n">
-        <v>1080</v>
+        <v>3080</v>
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
-        <v>1085</v>
+        <v>3085</v>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
     </row>
     <row r="80">
       <c r="A80" s="5" t="n">
-        <v>1100</v>
+        <v>3100</v>
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
-        <v>1105</v>
+        <v>3105</v>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
     </row>
     <row r="82">
       <c r="A82" s="5" t="n">
-        <v>1110</v>
+        <v>3110</v>
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
     </row>
     <row r="83">
       <c r="A83" s="3" t="n">
-        <v>1120</v>
+        <v>3120</v>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
     </row>
     <row r="84">
       <c r="A84" s="5" t="n">
-        <v>1121</v>
+        <v>3121</v>
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
-        <v>1125</v>
+        <v>3125</v>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
     </row>
     <row r="86">
       <c r="A86" s="5" t="n">
-        <v>1150</v>
+        <v>3150</v>
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
@@ -3298,7 +3298,7 @@
     </row>
     <row r="87">
       <c r="A87" s="3" t="n">
-        <v>1151</v>
+        <v>3151</v>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
     </row>
     <row r="88">
       <c r="A88" s="5" t="n">
-        <v>1160</v>
+        <v>3160</v>
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
     </row>
     <row r="89">
       <c r="A89" s="3" t="n">
-        <v>1170</v>
+        <v>3170</v>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
     </row>
     <row r="90">
       <c r="A90" s="5" t="n">
-        <v>1200</v>
+        <v>3200</v>
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
     </row>
     <row r="91">
       <c r="A91" s="3" t="n">
-        <v>1201</v>
+        <v>3201</v>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
     </row>
     <row r="92">
       <c r="A92" s="5" t="n">
-        <v>1205</v>
+        <v>3205</v>
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
     </row>
     <row r="93">
       <c r="A93" s="3" t="n">
-        <v>1210</v>
+        <v>3210</v>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
     </row>
     <row r="94">
       <c r="A94" s="5" t="n">
-        <v>1300</v>
+        <v>3300</v>
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
     </row>
     <row r="95">
       <c r="A95" s="3" t="n">
-        <v>1301</v>
+        <v>3301</v>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
     </row>
     <row r="96">
       <c r="A96" s="5" t="n">
-        <v>1302</v>
+        <v>3302</v>
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
     </row>
     <row r="97">
       <c r="A97" s="3" t="n">
-        <v>1303</v>
+        <v>3303</v>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
     </row>
     <row r="98">
       <c r="A98" s="5" t="n">
-        <v>1304</v>
+        <v>3304</v>
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
@@ -3694,7 +3694,7 @@
     </row>
     <row r="99">
       <c r="A99" s="3" t="n">
-        <v>1305</v>
+        <v>3305</v>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
     </row>
     <row r="100">
       <c r="A100" s="5" t="n">
-        <v>1320</v>
+        <v>3320</v>
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
     </row>
     <row r="101">
       <c r="A101" s="3" t="n">
-        <v>1325</v>
+        <v>3325</v>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
     </row>
     <row r="102">
       <c r="A102" s="5" t="n">
-        <v>1330</v>
+        <v>3330</v>
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
     </row>
     <row r="103">
       <c r="A103" s="3" t="n">
-        <v>1335</v>
+        <v>3335</v>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
     </row>
     <row r="104">
       <c r="A104" s="5" t="n">
-        <v>1400</v>
+        <v>3400</v>
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
@@ -3892,7 +3892,7 @@
     </row>
     <row r="105">
       <c r="A105" s="3" t="n">
-        <v>1401</v>
+        <v>3401</v>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
     </row>
     <row r="106">
       <c r="A106" s="5" t="n">
-        <v>1402</v>
+        <v>3402</v>
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
     </row>
     <row r="107">
       <c r="A107" s="3" t="n">
-        <v>1403</v>
+        <v>3403</v>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
     </row>
     <row r="108">
       <c r="A108" s="5" t="n">
-        <v>1404</v>
+        <v>3404</v>
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
@@ -4024,7 +4024,7 @@
     </row>
     <row r="109">
       <c r="A109" s="3" t="n">
-        <v>1405</v>
+        <v>3405</v>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
@@ -4057,7 +4057,7 @@
     </row>
     <row r="110">
       <c r="A110" s="5" t="n">
-        <v>1406</v>
+        <v>3406</v>
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
@@ -4090,7 +4090,7 @@
     </row>
     <row r="111">
       <c r="A111" s="3" t="n">
-        <v>1407</v>
+        <v>3407</v>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
     </row>
     <row r="112">
       <c r="A112" s="5" t="n">
-        <v>1408</v>
+        <v>3408</v>
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
     </row>
     <row r="113">
       <c r="A113" s="3" t="n">
-        <v>1409</v>
+        <v>3409</v>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
     </row>
     <row r="114">
       <c r="A114" s="5" t="n">
-        <v>1410</v>
+        <v>3410</v>
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
     </row>
     <row r="115">
       <c r="A115" s="3" t="n">
-        <v>1411</v>
+        <v>3411</v>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
     </row>
     <row r="116">
       <c r="A116" s="5" t="n">
-        <v>1412</v>
+        <v>3412</v>
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
     </row>
     <row r="117">
       <c r="A117" s="3" t="n">
-        <v>1413</v>
+        <v>3413</v>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
     </row>
     <row r="118">
       <c r="A118" s="5" t="n">
-        <v>1414</v>
+        <v>3414</v>
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
     </row>
     <row r="119">
       <c r="A119" s="3" t="n">
-        <v>1450</v>
+        <v>3450</v>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
     </row>
     <row r="120">
       <c r="A120" s="5" t="n">
-        <v>1451</v>
+        <v>3451</v>
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
     </row>
     <row r="121">
       <c r="A121" s="3" t="n">
-        <v>1460</v>
+        <v>3460</v>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
     </row>
     <row r="122">
       <c r="A122" s="5" t="n">
-        <v>1461</v>
+        <v>3461</v>
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
@@ -4486,7 +4486,7 @@
     </row>
     <row r="123">
       <c r="A123" s="3" t="n">
-        <v>1462</v>
+        <v>3462</v>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
     </row>
     <row r="124">
       <c r="A124" s="5" t="n">
-        <v>1463</v>
+        <v>3463</v>
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
     </row>
     <row r="125">
       <c r="A125" s="3" t="n">
-        <v>1500</v>
+        <v>3500</v>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
@@ -4585,7 +4585,7 @@
     </row>
     <row r="126">
       <c r="A126" s="5" t="n">
-        <v>1501</v>
+        <v>3501</v>
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
@@ -4618,7 +4618,7 @@
     </row>
     <row r="127">
       <c r="A127" s="3" t="n">
-        <v>1550</v>
+        <v>3550</v>
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
     </row>
     <row r="128">
       <c r="A128" s="5" t="n">
-        <v>1551</v>
+        <v>3551</v>
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
@@ -4684,7 +4684,7 @@
     </row>
     <row r="129">
       <c r="A129" s="3" t="n">
-        <v>1552</v>
+        <v>3552</v>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
@@ -4717,7 +4717,7 @@
     </row>
     <row r="130">
       <c r="A130" s="5" t="n">
-        <v>1553</v>
+        <v>3553</v>
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
     </row>
     <row r="131">
       <c r="A131" s="3" t="n">
-        <v>1554</v>
+        <v>3554</v>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
     </row>
     <row r="132">
       <c r="A132" s="5" t="n">
-        <v>1555</v>
+        <v>3555</v>
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
     </row>
     <row r="133">
       <c r="A133" s="3" t="n">
-        <v>1560</v>
+        <v>3560</v>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
     </row>
     <row r="134">
       <c r="A134" s="5" t="n">
-        <v>1561</v>
+        <v>3561</v>
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
